--- a/excel/production.xlsx
+++ b/excel/production.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Produksi\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4344C3C-FB09-422C-850E-76545ED3CEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679D0401-7A5B-4645-AE4B-90094E2531F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E7C73687-BEF7-4CA9-BF73-E0F83229CF68}"/>
   </bookViews>
@@ -943,6 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C4E9C-2505-47CE-8456-8945E3E53FEE}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:CK32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
